--- a/data/NAVARIS_3Part_AgreementFirst_OS.xlsx
+++ b/data/NAVARIS_3Part_AgreementFirst_OS.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MASTER_3Part_Agreement_First" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Agreement_First_Template" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Demand" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NAVARIS_Services" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Supplier" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="GitHub_ChatGPT_Setup" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="MASTER_3Part_Agreement_First" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Agreement_First_Template" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Demand" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="NAVARIS_Services" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Supplier" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="GitHub_ChatGPT_Setup" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -905,9 +905,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -915,9 +913,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-    </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -946,9 +942,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
@@ -956,9 +950,7 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -966,9 +958,7 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-    </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -1039,9 +1029,7 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" t="inlineStr"/>
-    </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
@@ -1681,9 +1669,7 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-    </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1691,9 +1677,7 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr"/>
-    </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -1722,9 +1706,7 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-    </row>
+    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
@@ -1767,9 +1749,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
@@ -1784,9 +1764,7 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-    </row>
+    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>

--- a/data/NAVARIS_3Part_AgreementFirst_OS.xlsx
+++ b/data/NAVARIS_3Part_AgreementFirst_OS.xlsx
@@ -905,7 +905,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -913,7 +912,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -942,7 +940,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
@@ -950,7 +947,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -958,7 +954,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -1029,7 +1024,6 @@
         </is>
       </c>
     </row>
-    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
@@ -1669,7 +1663,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
@@ -1677,7 +1670,6 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
@@ -1706,7 +1698,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
@@ -1749,7 +1740,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
@@ -1764,7 +1754,6 @@
         </is>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
